--- a/modules/catdriver/docs/templates/CatDriver_Config_Template.xlsx
+++ b/modules/catdriver/docs/templates/CatDriver_Config_Template.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Variables" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Driver_Settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Slides" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
   <si>
     <t xml:space="preserve">TURAS Catdriver Module - Settings</t>
   </si>
@@ -244,6 +245,18 @@
     <t xml:space="preserve">Generate an interactive HTML report alongside the Excel output.</t>
   </si>
   <si>
+    <t xml:space="preserve">Generate_Stats_Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility — designed for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y or N</t>
+  </si>
+  <si>
     <t xml:space="preserve">probability_lifts</t>
   </si>
   <si>
@@ -304,6 +317,27 @@
     <t xml:space="preserve">Researcher or agency name displayed in the HTML report footer.</t>
   </si>
   <si>
+    <t xml:space="preserve">slide_image_dir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directory containing slide images. Helps resolve relative image paths in the Slides sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directory path (absolute or relative to config file)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">custom_disclaimer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom text for the report footer disclaimer. Replaces the default disclaimer if provided.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">custom_footer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Custom footer text displayed at the bottom of the HTML report.</t>
+  </si>
+  <si>
     <t xml:space="preserve">SUBGROUP</t>
   </si>
   <si>
@@ -328,6 +362,27 @@
     <t xml:space="preserve">Include the total (all subgroups combined) analysis alongside subgroup-specific results.</t>
   </si>
   <si>
+    <t xml:space="preserve">STUDY IDENTIFICATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project name — appears in the stats pack Declaration sheet for identification and sign-off purposes. Leave blank if not using stats pack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst name — appears in the stats pack Declaration sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research_House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research organisation name — appears in the stats pack Declaration sheet. Use your company or white-label partner name.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TURAS Catdriver Module - Variables</t>
   </si>
   <si>
@@ -461,6 +516,57 @@
   </si>
   <si>
     <t xml:space="preserve">Negative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TURAS Catdriver Module - Slides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Define custom presentation slides for the HTML report. Supports markdown content and embedded images.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slide_order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slide_title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slide_content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slide_image_path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Order of the slide in the presentation (1, 2, 3...). Must be a whole number &gt;= 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Title displayed on the slide card. Keep concise for best appearance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Markdown content for the slide body. Supports **bold**, *italic*, ## heading, - bullet, &gt; quote.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Optional] Path to an image file (PNG, JPG) to embed in the slide. Will be base64 encoded. Relative paths resolved against slide_image_dir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Executive Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">## Key Findings
+- **Service quality** is the strongest driver of satisfaction
+- Price perception has a *moderate* positive effect
+&gt; Overall model explains 72% of variance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methodology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The analysis uses categorical key driver modelling with:
+- Ordinal logistic regression
+- SHAP-based importance decomposition
+- Bootstrap confidence intervals (n=500)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images/methodology_diagram.png</t>
   </si>
 </sst>
 </file>
@@ -1407,33 +1513,33 @@
         <v>76</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34">
@@ -1458,21 +1564,21 @@
         <v>86</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>14</v>
@@ -1481,15 +1587,15 @@
         <v>4</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>14</v>
@@ -1498,15 +1604,15 @@
         <v>4</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>14</v>
@@ -1515,24 +1621,32 @@
         <v>4</v>
       </c>
       <c r="D38" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="E38" s="14" t="s">
-        <v>88</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
+      <c r="A39" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>14</v>
@@ -1541,48 +1655,168 @@
         <v>4</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>30</v>
+        <v>103</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B42" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E42" s="14" t="s">
+      <c r="C46" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E46" s="14" t="s">
         <v>42</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
@@ -1593,7 +1827,8 @@
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A47:E47"/>
   </mergeCells>
   <dataValidations count="7">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20:B20">
@@ -1620,7 +1855,7 @@
       <formula1>50</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B41:B41">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45:B45">
       <formula1>10</formula1>
       <formula2>10000</formula2>
     </dataValidation>
@@ -1629,7 +1864,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="10">
         <x14:dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"binary,ordinal,multinomial"</xm:f>
@@ -1674,7 +1909,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"TRUE,FALSE"</xm:f>
+            <xm:f>"Y,N"</xm:f>
           </x14:formula1>
           <xm:sqref>B32:B32</xm:sqref>
         </x14:dataValidation>
@@ -1682,7 +1917,13 @@
           <x14:formula1>
             <xm:f>"TRUE,FALSE"</xm:f>
           </x14:formula1>
-          <xm:sqref>B42:B42</xm:sqref>
+          <xm:sqref>B33:B33</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"TRUE,FALSE"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B46:B46</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1703,107 +1944,107 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>14</v>
@@ -2026,29 +2267,29 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>44</v>
@@ -2056,39 +2297,39 @@
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>14</v>
@@ -2096,19 +2337,19 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>14</v>
@@ -2116,19 +2357,19 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="F7" s="17" t="s">
         <v>14</v>
@@ -2326,4 +2567,217 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="14.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="30.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="60.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="40.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="whole" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" sqref="A5:A26">
+      <formula1>1</formula1>
+      <formula2>999</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>